--- a/data-raw/doc/plaatjes/Afvoer Qafv_100jrTN2uur.xlsx
+++ b/data-raw/doc/plaatjes/Afvoer Qafv_100jrTN2uur.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C874B0A4-B80C-494F-9D05-2543558E61EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2715894F-EB6C-4937-88B9-DD19B33827BC}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{C874B0A4-B80C-494F-9D05-2543558E61EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1414B02A-C0C3-47D7-BDD4-0196CA473653}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>projectgebied</t>
   </si>
@@ -34,115 +35,121 @@
     <t>Qafv_100jrTN2uur_t=0</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=1</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=10</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=11</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=12</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=13</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=14</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=15</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=16</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=17</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=18</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=19</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=2</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=20</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=21</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=22</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=23</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=24</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=25</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=26</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=27</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=28</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=29</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=3</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=30</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=31</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=32</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=33</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=34</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=35</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=4</t>
-  </si>
-  <si>
     <t>Qafv_100jrTN2uur_t=5</t>
   </si>
   <si>
-    <t>Qafv_100jrTN2uur_t=6</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=7</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=8</t>
-  </si>
-  <si>
-    <t>Qafv_100jrTN2uur_t=9</t>
-  </si>
-  <si>
     <t>Tijd (u)</t>
   </si>
   <si>
     <t>Afvoer (m3/s)</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=100</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=105</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=110</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=115</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=120</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=125</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=130</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=135</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=140</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=145</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=150</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=155</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=160</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=165</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=170</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=175</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=180</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=185</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=40</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=45</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=50</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=55</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=60</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=65</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=70</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=75</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=80</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=85</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=90</t>
+  </si>
+  <si>
+    <t>Qafv_100jrTN2uur_t=95</t>
   </si>
 </sst>
 </file>
@@ -155,12 +162,18 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -175,8 +188,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -299,234 +313,246 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'1'!$B$2:$B$37</c:f>
+              <c:f>'1'!$B$2:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>18</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>19</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>22</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>23</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>24</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>25</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>26</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>27</c:v>
+                  <c:v>135</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>28</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>29</c:v>
+                  <c:v>145</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>30</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>31</c:v>
+                  <c:v>155</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>32</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>33</c:v>
+                  <c:v>165</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>34</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>35</c:v>
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'1'!$C$2:$C$37</c:f>
+              <c:f>'1'!$C$2:$C$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4118850702464396</c:v>
+                  <c:v>8.7413851088279308</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.7126405335549908</c:v>
+                  <c:v>10.441270755120801</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.1239150937808</c:v>
+                  <c:v>8.5154101848115893</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.666235445510701</c:v>
+                  <c:v>6.0194696936016996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16.325666804769099</c:v>
+                  <c:v>4.2009054779926904</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17.1662880463699</c:v>
+                  <c:v>2.9134832525922798</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17.261173710252901</c:v>
+                  <c:v>2.03827414316472</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16.810101397524601</c:v>
+                  <c:v>1.5025120935663401</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.8938665261291</c:v>
+                  <c:v>1.1938548238785101</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.680146730873201</c:v>
+                  <c:v>0.98799377044286996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.3004120222314</c:v>
+                  <c:v>0.84491587414469105</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.9171506047481</c:v>
+                  <c:v>0.73711225107021305</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10.610376195826801</c:v>
+                  <c:v>0.65129950682522098</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.3947836286713198</c:v>
+                  <c:v>0.57868904124114695</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.2959117627365497</c:v>
+                  <c:v>0.51345496285165204</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.3191241101509599</c:v>
+                  <c:v>0.45524786749920199</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.4421052769091602</c:v>
+                  <c:v>0.40260781812420299</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.6670179925106101</c:v>
+                  <c:v>0.35512823340125899</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.99054018783161</c:v>
+                  <c:v>0.31225891474135098</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.4010935464280996</c:v>
+                  <c:v>0.27318845515024198</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.8747099225277299</c:v>
+                  <c:v>0.23753888932014899</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.42296502829045</c:v>
+                  <c:v>0.20515946104073801</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.0503016539519101</c:v>
+                  <c:v>0.17537552963698599</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.7406507612741202</c:v>
+                  <c:v>0.148182124954332</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.4785292956106302</c:v>
+                  <c:v>0.123815768903823</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.2556086638237498</c:v>
+                  <c:v>0.10236742316576999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.0676131307089101</c:v>
+                  <c:v>8.3705538255555101E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.91557533211446</c:v>
+                  <c:v>6.7594255767762595E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.78449237150724</c:v>
+                  <c:v>5.38494900006386E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.66976186218379</c:v>
+                  <c:v>4.2393846673374799E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.56860646237947</c:v>
+                  <c:v>3.3116787789765997E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.47708320728054</c:v>
+                  <c:v>2.5769838650247401E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.3927817003607501</c:v>
+                  <c:v>2.0198750796460298E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.31547619492088</c:v>
+                  <c:v>1.57536344584524E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.24333997988664</c:v>
+                  <c:v>1.2169380290139101E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>9.3609244454315593E-3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.38493113814834E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1670,25 +1696,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Blad1"/>
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="15" max="16" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1699,394 +1726,419 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>8.7413851088279308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10.441270755120801</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>4.4118850702464396</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>8.5154101848115893</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6.0194696936016996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>4.2009054779926904</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.9134832525922798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>2.03827414316472</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.5025120935663401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>45</v>
+      </c>
+      <c r="C11">
+        <v>1.1938548238785101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>0.98799377044286996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>55</v>
+      </c>
+      <c r="C13">
+        <v>0.84491587414469105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>0.73711225107021305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15">
+        <v>65</v>
+      </c>
+      <c r="C15">
+        <v>0.65129950682522098</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>70</v>
+      </c>
+      <c r="C16">
+        <v>0.57868904124114695</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>75</v>
+      </c>
+      <c r="C17">
+        <v>0.51345496285165204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18">
+        <v>80</v>
+      </c>
+      <c r="C18">
+        <v>0.45524786749920199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <v>85</v>
+      </c>
+      <c r="C19">
+        <v>0.40260781812420299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20">
+        <v>90</v>
+      </c>
+      <c r="C20">
+        <v>0.35512823340125899</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21">
+        <v>95</v>
+      </c>
+      <c r="C21">
+        <v>0.31225891474135098</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>0.27318845515024198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>105</v>
+      </c>
+      <c r="C23">
+        <v>0.23753888932014899</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>8.7126405335549908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B24">
+        <v>110</v>
+      </c>
+      <c r="C24">
+        <v>0.20515946104073801</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25">
+        <v>115</v>
+      </c>
+      <c r="C25">
+        <v>0.17537552963698599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>120</v>
+      </c>
+      <c r="C26">
+        <v>0.148182124954332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27">
+        <v>125</v>
+      </c>
+      <c r="C27">
+        <v>0.123815768903823</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>130</v>
+      </c>
+      <c r="C28">
+        <v>0.10236742316576999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>135</v>
+      </c>
+      <c r="C29">
+        <v>8.3705538255555101E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>140</v>
+      </c>
+      <c r="C30">
+        <v>6.7594255767762595E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>145</v>
+      </c>
+      <c r="C31">
+        <v>5.38494900006386E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>150</v>
+      </c>
+      <c r="C32">
+        <v>4.2393846673374799E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>155</v>
+      </c>
+      <c r="C33">
+        <v>3.3116787789765997E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34">
+        <v>160</v>
+      </c>
+      <c r="C34">
+        <v>2.5769838650247401E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>24</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>12.1239150937808</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>14.666235445510701</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>16.325666804769099</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>17.1662880463699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>17.261173710252901</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10">
-        <v>16.810101397524601</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11">
-        <v>15.8938665261291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>14.680146730873201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>13.3004120222314</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14">
-        <v>11.9171506047481</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15">
-        <v>10.610376195826801</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16">
-        <v>14</v>
-      </c>
-      <c r="C16">
-        <v>9.3947836286713198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17">
-        <v>8.2959117627365497</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18">
-        <v>7.3191241101509599</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19">
-        <v>17</v>
-      </c>
-      <c r="C19">
-        <v>6.4421052769091602</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20">
-        <v>18</v>
-      </c>
-      <c r="C20">
-        <v>5.6670179925106101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21">
-        <v>19</v>
-      </c>
-      <c r="C21">
-        <v>4.99054018783161</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22">
-        <v>20</v>
-      </c>
-      <c r="C22">
-        <v>4.4010935464280996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23">
-        <v>21</v>
-      </c>
-      <c r="C23">
-        <v>3.8747099225277299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24">
-        <v>22</v>
-      </c>
-      <c r="C24">
-        <v>3.42296502829045</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25">
-        <v>23</v>
-      </c>
-      <c r="C25">
-        <v>3.0503016539519101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26">
-        <v>24</v>
-      </c>
-      <c r="C26">
-        <v>2.7406507612741202</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27">
+      <c r="B35">
+        <v>165</v>
+      </c>
+      <c r="C35">
+        <v>2.0198750796460298E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>25</v>
       </c>
-      <c r="C27">
-        <v>2.4785292956106302</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28">
+      <c r="B36">
+        <v>170</v>
+      </c>
+      <c r="C36">
+        <v>1.57536344584524E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>26</v>
       </c>
-      <c r="C28">
-        <v>2.2556086638237498</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29">
+      <c r="B37">
+        <v>175</v>
+      </c>
+      <c r="C37">
+        <v>1.2169380290139101E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>27</v>
       </c>
-      <c r="C29">
-        <v>2.0676131307089101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30">
+      <c r="B38">
+        <v>180</v>
+      </c>
+      <c r="C38">
+        <v>9.3609244454315593E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>28</v>
       </c>
-      <c r="C30">
-        <v>1.91557533211446</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31">
-        <v>29</v>
-      </c>
-      <c r="C31">
-        <v>1.78449237150724</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32">
-        <v>30</v>
-      </c>
-      <c r="C32">
-        <v>1.66976186218379</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33">
-        <v>31</v>
-      </c>
-      <c r="C33">
-        <v>1.56860646237947</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>1.47708320728054</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35">
-        <v>33</v>
-      </c>
-      <c r="C35">
-        <v>1.3927817003607501</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36">
-        <v>34</v>
-      </c>
-      <c r="C36">
-        <v>1.31547619492088</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37">
-        <v>35</v>
-      </c>
-      <c r="C37">
-        <v>1.24333997988664</v>
+      <c r="B39">
+        <v>185</v>
+      </c>
+      <c r="C39">
+        <v>7.38493113814834E-3</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C38">
-    <sortCondition ref="B2:B38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O3:Q40">
+    <sortCondition ref="P3:P40"/>
   </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="1.2204724409448819" bottom="0.98425196850393704" header="0.6692913385826772" footer="0.43307086614173229"/>
@@ -2104,14 +2156,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[{"colorTheme":"{{DataSources.ColorThemes[\"Sweco\"].ColorTheme}}","disableUpdates":false,"type":"colorTheme"}],"templateName":"Blank","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[{"colorTheme":"{{DataSources.ColorThemes[\"Sweco\"].ColorTheme}}","disableUpdates":false,"type":"colorTheme"}],"templateName":"Blank","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="dokument" ma:contentTypeID="0x010100BA85B17551307B4383D2980D4EFA5515" ma:contentTypeVersion="12" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="57aaa53a121281638ac8bc132f802243">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="173d6b2f-59a8-488e-935d-67e78bda59e5" xmlns:ns3="b97dc65e-fe16-4df7-925c-ff3316bf7bf3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="141727366efbfc4d0736cea1f099176a" ns2:_="" ns3:_="">
     <xsd:import namespace="173d6b2f-59a8-488e-935d-67e78bda59e5"/>
@@ -2328,34 +2395,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDDE50B2-2507-4A17-8842-A7EE75090943}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C2894E-68C9-476D-803E-814AC6EBDDB7}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDDE50B2-2507-4A17-8842-A7EE75090943}">
-  <ds:schemaRefs/>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79BD3FF0-C90B-4BBB-AF14-2B7944CED71E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe0e463f-46c1-4b5a-aeae-2e65b5901510"/>
+  </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B094B8C0-0888-4622-A87D-10D4D23C20D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{754B3D83-15E4-4B5F-8568-57884EBAF882}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2372,22 +2442,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B094B8C0-0888-4622-A87D-10D4D23C20D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79BD3FF0-C90B-4BBB-AF14-2B7944CED71E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe0e463f-46c1-4b5a-aeae-2e65b5901510"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>